--- a/fish ai variable.xlsx
+++ b/fish ai variable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>鱼类名称</t>
   </si>
@@ -49,9 +49,15 @@
     <t>dur1Max</t>
   </si>
   <si>
+    <t>dur2Min</t>
+  </si>
+  <si>
     <t>dur2Max</t>
   </si>
   <si>
+    <t>dur3Min</t>
+  </si>
+  <si>
     <t>dur3Max</t>
   </si>
   <si>
@@ -155,6 +161,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>海鲇</t>
     </r>
     <r>
@@ -200,6 +213,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>金鲳鱼</t>
     </r>
     <r>
@@ -236,6 +256,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>鲭</t>
     </r>
     <r>
@@ -321,6 +348,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>‌</t>
     </r>
     <r>
@@ -1352,54 +1386,54 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" ht="15" spans="1:21">
       <c r="A2" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2" s="6">
         <v>0.7</v>
@@ -1464,7 +1498,7 @@
     </row>
     <row r="3" ht="15" spans="1:21">
       <c r="A3" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" s="6">
         <v>0.5</v>
@@ -1529,7 +1563,7 @@
     </row>
     <row r="4" ht="15" spans="1:21">
       <c r="A4" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B4" s="6">
         <v>0.25</v>
@@ -1594,7 +1628,7 @@
     </row>
     <row r="5" ht="15" spans="1:21">
       <c r="A5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" s="6">
         <v>0.6</v>
@@ -1659,7 +1693,7 @@
     </row>
     <row r="6" ht="15" spans="1:21">
       <c r="A6" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="6">
         <v>0.9</v>
@@ -1724,7 +1758,7 @@
     </row>
     <row r="7" ht="15" spans="1:21">
       <c r="A7" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" s="6">
         <v>0.9</v>
@@ -1789,7 +1823,7 @@
     </row>
     <row r="8" ht="15" spans="1:21">
       <c r="A8" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B8" s="6">
         <v>0.9</v>
@@ -1854,7 +1888,7 @@
     </row>
     <row r="9" ht="15" spans="1:21">
       <c r="A9" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B9" s="6">
         <v>0.6</v>
@@ -1919,7 +1953,7 @@
     </row>
     <row r="10" ht="15" spans="1:21">
       <c r="A10" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B10" s="6">
         <v>0.6</v>
@@ -1984,7 +2018,7 @@
     </row>
     <row r="11" ht="15" spans="1:21">
       <c r="A11" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" s="6">
         <v>0.5</v>
@@ -2049,7 +2083,7 @@
     </row>
     <row r="12" ht="15" spans="1:21">
       <c r="A12" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B12" s="6">
         <v>0.6</v>
@@ -2114,7 +2148,7 @@
     </row>
     <row r="13" ht="15" spans="1:21">
       <c r="A13" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="6">
         <v>0.9</v>
@@ -2179,7 +2213,7 @@
     </row>
     <row r="14" ht="15" spans="1:21">
       <c r="A14" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B14" s="6">
         <v>0.5</v>
@@ -2244,7 +2278,7 @@
     </row>
     <row r="15" ht="15" spans="1:21">
       <c r="A15" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" s="6">
         <v>0.9</v>
@@ -2309,7 +2343,7 @@
     </row>
     <row r="16" ht="15" spans="1:21">
       <c r="A16" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B16" s="6">
         <v>0.5</v>
@@ -2374,7 +2408,7 @@
     </row>
     <row r="17" ht="15" spans="1:21">
       <c r="A17" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B17" s="6">
         <v>0.9</v>
@@ -2439,7 +2473,7 @@
     </row>
     <row r="18" ht="15" spans="1:21">
       <c r="A18" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B18" s="6">
         <v>0.5</v>
@@ -2504,7 +2538,7 @@
     </row>
     <row r="19" ht="15" spans="1:21">
       <c r="A19" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B19" s="6">
         <v>0.5</v>
@@ -2569,7 +2603,7 @@
     </row>
     <row r="20" ht="15" spans="1:21">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="6">
         <v>0.9</v>
@@ -2634,7 +2668,7 @@
     </row>
     <row r="21" ht="15" spans="1:21">
       <c r="A21" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B21" s="6">
         <v>0.9</v>
@@ -2699,7 +2733,7 @@
     </row>
     <row r="22" ht="15" spans="1:21">
       <c r="A22" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B22" s="6">
         <v>0.4</v>
@@ -2764,7 +2798,7 @@
     </row>
     <row r="23" ht="15" spans="1:21">
       <c r="A23" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B23" s="6">
         <v>0.5</v>
@@ -2829,7 +2863,7 @@
     </row>
     <row r="24" ht="15" spans="1:21">
       <c r="A24" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B24" s="6">
         <v>0.9</v>
@@ -2894,7 +2928,7 @@
     </row>
     <row r="25" ht="15" spans="1:21">
       <c r="A25" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B25" s="6">
         <v>0.5</v>
@@ -2959,7 +2993,7 @@
     </row>
     <row r="26" ht="15" spans="1:21">
       <c r="A26" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B26" s="6">
         <v>0.6</v>
@@ -3024,7 +3058,7 @@
     </row>
     <row r="27" ht="15" spans="1:21">
       <c r="A27" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B27" s="6">
         <v>0.9</v>
@@ -3089,7 +3123,7 @@
     </row>
     <row r="28" ht="15" spans="1:21">
       <c r="A28" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B28" s="6">
         <v>0.9</v>
@@ -3154,7 +3188,7 @@
     </row>
     <row r="29" ht="15" spans="1:21">
       <c r="A29" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B29" s="6">
         <v>0.4</v>
@@ -3219,7 +3253,7 @@
     </row>
     <row r="30" ht="15" spans="1:21">
       <c r="A30" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B30" s="6">
         <v>0.9</v>
@@ -3284,7 +3318,7 @@
     </row>
     <row r="31" ht="15" spans="1:21">
       <c r="A31" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B31" s="6">
         <v>0.6</v>
@@ -3313,7 +3347,9 @@
       <c r="J31" s="7">
         <v>1.5</v>
       </c>
-      <c r="K31" s="7"/>
+      <c r="K31" s="7">
+        <v>1</v>
+      </c>
       <c r="L31" s="7">
         <v>130</v>
       </c>
@@ -3347,7 +3383,7 @@
     </row>
     <row r="32" ht="15" spans="1:21">
       <c r="A32" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B32" s="6">
         <v>0.6</v>
@@ -3412,7 +3448,7 @@
     </row>
     <row r="33" ht="15" spans="1:21">
       <c r="A33" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B33" s="6">
         <v>0.6</v>
@@ -3477,7 +3513,7 @@
     </row>
     <row r="34" ht="15" spans="1:21">
       <c r="A34" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B34" s="6">
         <v>1</v>
@@ -3542,7 +3578,7 @@
     </row>
     <row r="35" ht="15" spans="1:21">
       <c r="A35" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B35" s="6">
         <v>0.6</v>
@@ -3607,7 +3643,7 @@
     </row>
     <row r="36" ht="15" spans="1:21">
       <c r="A36" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B36" s="6">
         <v>0.4</v>
@@ -3672,7 +3708,7 @@
     </row>
     <row r="37" ht="15" spans="1:21">
       <c r="A37" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B37" s="6">
         <v>0.9</v>
@@ -3737,7 +3773,7 @@
     </row>
     <row r="38" ht="15" spans="1:21">
       <c r="A38" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B38" s="6">
         <v>1</v>
@@ -3802,7 +3838,7 @@
     </row>
     <row r="39" ht="15" spans="1:21">
       <c r="A39" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B39" s="6">
         <v>0.6</v>
@@ -3867,7 +3903,7 @@
     </row>
     <row r="40" ht="15" spans="1:21">
       <c r="A40" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B40" s="6">
         <v>0.5</v>
@@ -3932,7 +3968,7 @@
     </row>
     <row r="41" ht="15" spans="1:21">
       <c r="A41" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B41" s="6">
         <v>0.9</v>
@@ -3997,7 +4033,7 @@
     </row>
     <row r="42" ht="15" spans="1:21">
       <c r="A42" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B42" s="6">
         <v>0.9</v>
@@ -4062,7 +4098,7 @@
     </row>
     <row r="43" ht="15" spans="1:21">
       <c r="A43" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B43" s="6">
         <v>0.6</v>
@@ -4127,7 +4163,7 @@
     </row>
     <row r="44" ht="15" spans="1:21">
       <c r="A44" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B44" s="6">
         <v>0.9</v>
@@ -4192,7 +4228,7 @@
     </row>
     <row r="45" ht="15" spans="1:21">
       <c r="A45" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B45" s="6">
         <v>1</v>
@@ -4257,7 +4293,7 @@
     </row>
     <row r="46" ht="15" spans="1:21">
       <c r="A46" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B46" s="6">
         <v>0.9</v>
@@ -4322,7 +4358,7 @@
     </row>
     <row r="47" ht="15" spans="1:21">
       <c r="A47" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B47" s="6">
         <v>0.9</v>
@@ -4387,7 +4423,7 @@
     </row>
     <row r="48" ht="15" spans="1:21">
       <c r="A48" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B48" s="6">
         <v>1</v>
@@ -4452,7 +4488,7 @@
     </row>
     <row r="49" ht="15" spans="1:21">
       <c r="A49" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B49" s="6">
         <v>0.9</v>
@@ -4517,7 +4553,7 @@
     </row>
     <row r="50" ht="15" spans="1:21">
       <c r="A50" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B50" s="6">
         <v>1</v>
@@ -4582,7 +4618,7 @@
     </row>
     <row r="51" ht="15" spans="1:21">
       <c r="A51" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B51" s="6">
         <v>0.9</v>
@@ -4647,7 +4683,7 @@
     </row>
     <row r="52" ht="15" spans="1:21">
       <c r="A52" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B52" s="6">
         <v>1</v>
@@ -4712,7 +4748,7 @@
     </row>
     <row r="53" ht="15" spans="1:21">
       <c r="A53" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B53" s="6">
         <v>0.9</v>
@@ -4777,7 +4813,7 @@
     </row>
     <row r="54" ht="15" spans="1:21">
       <c r="A54" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B54" s="6">
         <v>0.6</v>
@@ -4842,7 +4878,7 @@
     </row>
     <row r="55" ht="15" spans="1:21">
       <c r="A55" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B55" s="6">
         <v>1</v>
@@ -4907,7 +4943,7 @@
     </row>
     <row r="56" ht="15" spans="1:21">
       <c r="A56" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B56" s="6">
         <v>0.9</v>
@@ -4972,7 +5008,7 @@
     </row>
     <row r="57" ht="15" spans="1:21">
       <c r="A57" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B57" s="6">
         <v>0.9</v>
@@ -5037,7 +5073,7 @@
     </row>
     <row r="58" ht="15" spans="1:21">
       <c r="A58" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B58" s="6">
         <v>1</v>
@@ -5102,7 +5138,7 @@
     </row>
     <row r="59" ht="15" spans="1:21">
       <c r="A59" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B59" s="6">
         <v>0.9</v>
@@ -5167,7 +5203,7 @@
     </row>
     <row r="60" ht="15" spans="1:21">
       <c r="A60" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B60" s="6">
         <v>0.9</v>
@@ -5232,7 +5268,7 @@
     </row>
     <row r="61" ht="15" spans="1:21">
       <c r="A61" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B61" s="6">
         <v>0.6</v>
@@ -5297,7 +5333,7 @@
     </row>
     <row r="62" ht="15" spans="1:21">
       <c r="A62" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B62" s="6">
         <v>1</v>
@@ -5362,7 +5398,7 @@
     </row>
     <row r="63" ht="15" spans="1:21">
       <c r="A63" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B63" s="6">
         <v>1</v>
@@ -5427,7 +5463,7 @@
     </row>
     <row r="64" ht="15" spans="1:21">
       <c r="A64" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B64" s="6">
         <v>0.9</v>
@@ -5492,7 +5528,7 @@
     </row>
     <row r="65" ht="15" spans="1:21">
       <c r="A65" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B65" s="6">
         <v>0.6</v>
@@ -5557,7 +5593,7 @@
     </row>
     <row r="66" ht="15" spans="1:21">
       <c r="A66" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B66" s="6">
         <v>1</v>
@@ -5622,7 +5658,7 @@
     </row>
     <row r="67" ht="15" spans="1:21">
       <c r="A67" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B67" s="6">
         <v>0.6</v>
@@ -5687,7 +5723,7 @@
     </row>
     <row r="68" ht="15" spans="1:21">
       <c r="A68" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B68" s="6">
         <v>0.6</v>
